--- a/freelanceData.xlsx
+++ b/freelanceData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\Uni - Computer Science with Cyber Security\Stage 1\Term 1\IN1007 Creative Coding\Dear data 100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{273BED83-F2A8-4118-9690-1D21B97488F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C77D09-7DB9-4F44-BDEE-C64F66882DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{7A470A56-0B14-47BE-935A-900520D3C989}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7A470A56-0B14-47BE-935A-900520D3C989}"/>
   </bookViews>
   <sheets>
     <sheet name="freelanceDatav2" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
   <si>
     <t>shift</t>
   </si>
@@ -77,6 +77,33 @@
   </si>
   <si>
     <t>mapDifficulty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shift </t>
+  </si>
+  <si>
+    <t>quota</t>
+  </si>
+  <si>
+    <t>eggsCollected</t>
+  </si>
+  <si>
+    <t>paintedWalls</t>
+  </si>
+  <si>
+    <t>won</t>
+  </si>
+  <si>
+    <t>waitedForNewTeammates</t>
+  </si>
+  <si>
+    <t>checkedPerformanceInGame</t>
+  </si>
+  <si>
+    <t>checkedPerformanceInApp</t>
+  </si>
+  <si>
+    <t>blocked</t>
   </si>
 </sst>
 </file>
@@ -458,9 +485,543 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73422113-E1F7-496E-85DB-4F235896A772}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="5.1796875" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" customWidth="1"/>
+    <col min="7" max="7" width="8.1796875" customWidth="1"/>
+    <col min="8" max="8" width="11.36328125" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.08984375" customWidth="1"/>
+    <col min="11" max="11" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>6.5</v>
+      </c>
+      <c r="D2">
+        <v>400</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2.23</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>84</v>
+      </c>
+      <c r="K2">
+        <v>101</v>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>6.5</v>
+      </c>
+      <c r="D3">
+        <v>420</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>85</v>
+      </c>
+      <c r="K3">
+        <v>154</v>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>6.5</v>
+      </c>
+      <c r="D4">
+        <v>440</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2.67</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>90</v>
+      </c>
+      <c r="K4">
+        <v>115</v>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>6.5</v>
+      </c>
+      <c r="D5">
+        <v>460</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2.48</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>87</v>
+      </c>
+      <c r="K5">
+        <v>145</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>6.5</v>
+      </c>
+      <c r="D6">
+        <v>480</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2.68</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>90</v>
+      </c>
+      <c r="K6">
+        <v>109</v>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>6.5</v>
+      </c>
+      <c r="D7">
+        <v>500</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>85</v>
+      </c>
+      <c r="K7">
+        <v>95</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+      <c r="D8">
+        <v>500</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2.58</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>88</v>
+      </c>
+      <c r="K8">
+        <v>91</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>2</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>6.5</v>
+      </c>
+      <c r="D9">
+        <v>500</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2.74</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>90</v>
+      </c>
+      <c r="K9">
+        <v>147</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>6.5</v>
+      </c>
+      <c r="D10">
+        <v>520</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2.44</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>87</v>
+      </c>
+      <c r="K10">
+        <v>109</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>3</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>6.5</v>
+      </c>
+      <c r="D11">
+        <v>540</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2.46</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>87</v>
+      </c>
+      <c r="K11">
+        <v>109</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>3</v>
+      </c>
+      <c r="N11">
+        <v>2</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
